--- a/docs/Proyecto/Diccionario I.xlsx
+++ b/docs/Proyecto/Diccionario I.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mavillam\Documents\MIAD\Proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Docsmavillam\cursos\MISO-MIAD\MIAD\2220\CarpetaConTodoProyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D114D0E-294B-4109-8FE9-CA8E95650882}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
     <sheet name="Diccionario" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>Tabla</t>
   </si>
@@ -31,29 +30,200 @@
     <t>Descripcion</t>
   </si>
   <si>
-    <t>Unidades</t>
-  </si>
-  <si>
-    <t>°</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
-    <t>Este recurso estará disponible antes de que deba iniciar la tarea</t>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>UnidadDelLimite</t>
+  </si>
+  <si>
+    <t>EsEHB</t>
+  </si>
+  <si>
+    <t>EstaCubiertoPorSeguro</t>
+  </si>
+  <si>
+    <t>TieneLimiteCuantitativo</t>
+  </si>
+  <si>
+    <t>ExcluidoDelDesembolsoMaximoDentroDeLaRed</t>
+  </si>
+  <si>
+    <t>ExcluidoDelDesembolsoMaximoFueraDeLaRed</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Condado</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Densidad</t>
+  </si>
+  <si>
+    <t>Identificador del area de servicio</t>
+  </si>
+  <si>
+    <t>Nombre del área de servicio</t>
+  </si>
+  <si>
+    <t>Fecha de creación del área de servicio</t>
+  </si>
+  <si>
+    <t>Nombre del estado</t>
+  </si>
+  <si>
+    <t>Nombre del condado</t>
+  </si>
+  <si>
+    <t>Identificador del condado</t>
+  </si>
+  <si>
+    <t>area en millas cuadradas</t>
+  </si>
+  <si>
+    <t>numero de habitantes por milla cuadrada</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>identificador de la condicion de pago</t>
+  </si>
+  <si>
+    <t>descripción de la condición de pago como NoAplica, Después de deducible</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>identificador del plan</t>
+  </si>
+  <si>
+    <t>identificador del tipo de beneficio</t>
+  </si>
+  <si>
+    <t>identificador del área de servicio</t>
+  </si>
+  <si>
+    <t>identificador de la condicion de pago Copago</t>
+  </si>
+  <si>
+    <t>identificador de la condicion de pago Coseguro</t>
+  </si>
+  <si>
+    <t>Fecha de oferta del beneficio para ese plan</t>
+  </si>
+  <si>
+    <t>identificador del proveedor del plan</t>
+  </si>
+  <si>
+    <t>valor del copago</t>
+  </si>
+  <si>
+    <t>valor del coseguro</t>
+  </si>
+  <si>
+    <t>cantidad limite del tipo de beneficio</t>
+  </si>
+  <si>
+    <t>nombre del tipo de beneficio</t>
+  </si>
+  <si>
+    <t>unidad en la que se expresa el límite</t>
+  </si>
+  <si>
+    <t>Indica si tiene limiente cuantitativo</t>
+  </si>
+  <si>
+    <t>indica si está excluído del desembolso máximo dentro de la red</t>
+  </si>
+  <si>
+    <t>indica si está excluído del desembolso máximo fuera de la red</t>
+  </si>
+  <si>
+    <t>Indica si el seguor lo cubre</t>
+  </si>
+  <si>
+    <t>Es beneficio esencial de salud</t>
+  </si>
+  <si>
+    <t>FuenteAreasDeServicio_Copia_E</t>
+  </si>
+  <si>
+    <t>FuenteCondicionesDePago_Copia_E</t>
+  </si>
+  <si>
+    <t>FuentesPlanesBeneficio_Copia_E</t>
+  </si>
+  <si>
+    <t>FuenteTiposBeneficio_Copia_E</t>
+  </si>
+  <si>
+    <t>idAreaServicio_T</t>
+  </si>
+  <si>
+    <t>NombreAreaDeServicio</t>
+  </si>
+  <si>
+    <t>idGeografía_T</t>
+  </si>
+  <si>
+    <t>PoblacionAct</t>
+  </si>
+  <si>
+    <t>Número de habitantes actuales</t>
+  </si>
+  <si>
+    <t>idCondicionesDePago_T</t>
+  </si>
+  <si>
+    <t>Copago o Coseguro o Anticipado</t>
+  </si>
+  <si>
+    <t>idPlan_T</t>
+  </si>
+  <si>
+    <t>idTipoBeneficio_T</t>
+  </si>
+  <si>
+    <t>idAreaDeServicio_T</t>
+  </si>
+  <si>
+    <t>idCondicionesDePagoCopago_T</t>
+  </si>
+  <si>
+    <t>idCondicionesDePagoCoseguro_T</t>
+  </si>
+  <si>
+    <t>idProveedor_T</t>
+  </si>
+  <si>
+    <t>idNivelServicio_T</t>
+  </si>
+  <si>
+    <t>identificador del nivel de servicio</t>
+  </si>
+  <si>
+    <t>valorCopago</t>
+  </si>
+  <si>
+    <t>valorCoseguro</t>
+  </si>
+  <si>
+    <t>cantidadLimite</t>
+  </si>
+  <si>
+    <t>Fecha en que se definel el tipo de beneficio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -78,13 +248,55 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -96,10 +308,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,16 +329,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -337,23 +570,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1002"/>
+  <dimension ref="A1:D1011"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="154.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -365,403 +597,544 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
+      <c r="C27" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
+      <c r="C28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7" t="s">
+      <c r="C29" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="6"/>
-      <c r="D16" s="7" t="s">
+      <c r="C30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="6"/>
-    </row>
-    <row r="34" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
+      <c r="C31" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
       <c r="B35" s="6"/>
-    </row>
-    <row r="36" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="11"/>
       <c r="B36" s="6"/>
-    </row>
-    <row r="37" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="11"/>
       <c r="B37" s="6"/>
-    </row>
-    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="11"/>
       <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-    </row>
-    <row r="39" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="11"/>
       <c r="B39" s="6"/>
-    </row>
-    <row r="40" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="11"/>
       <c r="B40" s="6"/>
-    </row>
-    <row r="41" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A41" s="11"/>
       <c r="B41" s="6"/>
-    </row>
-    <row r="42" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="11"/>
       <c r="B42" s="6"/>
     </row>
-    <row r="43" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
+    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A43" s="11"/>
       <c r="B43" s="6"/>
     </row>
-    <row r="44" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="9"/>
+    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="11"/>
       <c r="B44" s="6"/>
     </row>
-    <row r="45" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A45" s="9"/>
+    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="11"/>
       <c r="B45" s="6"/>
     </row>
-    <row r="46" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A46" s="9"/>
+    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A46" s="11"/>
       <c r="B46" s="6"/>
     </row>
-    <row r="47" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A47" s="9"/>
+    <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
       <c r="B47" s="6"/>
-    </row>
-    <row r="48" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A48" s="9"/>
+      <c r="C47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A48" s="11"/>
       <c r="B48" s="6"/>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="9"/>
+      <c r="A49" s="11"/>
       <c r="B49" s="6"/>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="8"/>
+      <c r="A50" s="11"/>
       <c r="B50" s="6"/>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
+      <c r="A51" s="11"/>
       <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A52" s="9"/>
+      <c r="A52" s="11"/>
       <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A53" s="9"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="6"/>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A54" s="9"/>
+      <c r="A54" s="11"/>
       <c r="B54" s="6"/>
     </row>
-    <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
+    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
       <c r="B55" s="6"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
+    </row>
+    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="11"/>
       <c r="B56" s="6"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
+    </row>
+    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="11"/>
       <c r="B57" s="6"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="9"/>
+    </row>
+    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="11"/>
       <c r="B58" s="6"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="9"/>
+    </row>
+    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="10"/>
       <c r="B59" s="6"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="9"/>
+    </row>
+    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="11"/>
       <c r="B60" s="6"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-    </row>
-    <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
+    </row>
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="11"/>
       <c r="B61" s="6"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-    </row>
-    <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="9"/>
+    </row>
+    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="11"/>
       <c r="B62" s="6"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-    </row>
-    <row r="63" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="9"/>
+    </row>
+    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="11"/>
       <c r="B63" s="6"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A64" s="9"/>
+      <c r="A64" s="10"/>
       <c r="B64" s="6"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="9"/>
+      <c r="A65" s="11"/>
       <c r="B65" s="6"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="9"/>
+      <c r="A66" s="11"/>
       <c r="B66" s="6"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="9"/>
+      <c r="A67" s="11"/>
       <c r="B67" s="6"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
     </row>
-    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="5"/>
+    <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="11"/>
       <c r="B68" s="6"/>
-    </row>
-    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="5"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A69" s="11"/>
       <c r="B69" s="6"/>
-    </row>
-    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="5"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="11"/>
       <c r="B70" s="6"/>
-    </row>
-    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="5"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="11"/>
       <c r="B71" s="6"/>
-    </row>
-    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="5"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="11"/>
       <c r="B72" s="6"/>
-    </row>
-    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A73" s="5"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="11"/>
       <c r="B73" s="6"/>
-    </row>
-    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="5"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A74" s="11"/>
       <c r="B74" s="6"/>
-    </row>
-    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="5"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="11"/>
       <c r="B75" s="6"/>
-    </row>
-    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="5"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="11"/>
       <c r="B76" s="6"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5"/>
@@ -4467,16 +4840,56 @@
       <c r="A1002" s="5"/>
       <c r="B1002" s="6"/>
     </row>
+    <row r="1003" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1003" s="5"/>
+      <c r="B1003" s="6"/>
+    </row>
+    <row r="1004" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1004" s="5"/>
+      <c r="B1004" s="6"/>
+    </row>
+    <row r="1005" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1005" s="5"/>
+      <c r="B1005" s="6"/>
+    </row>
+    <row r="1006" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1006" s="5"/>
+      <c r="B1006" s="6"/>
+    </row>
+    <row r="1007" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1007" s="5"/>
+      <c r="B1007" s="6"/>
+    </row>
+    <row r="1008" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1008" s="5"/>
+      <c r="B1008" s="6"/>
+    </row>
+    <row r="1009" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1009" s="5"/>
+      <c r="B1009" s="6"/>
+    </row>
+    <row r="1010" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1010" s="5"/>
+      <c r="B1010" s="6"/>
+    </row>
+    <row r="1011" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1011" s="5"/>
+      <c r="B1011" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:A25"/>
-    <mergeCell ref="A26:A37"/>
-    <mergeCell ref="A38:A49"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="A55:A67"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A64:A76"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A25"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4670,14 +5083,14 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70188184-5602-41F6-A383-FA9EAECBDB93}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c05144fa-b45f-40a6-8288-53f00543b24f"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c05144fa-b45f-40a6-8288-53f00543b24f"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
